--- a/docs/validacao-visual/2026-10-vendas-precos-pvp-stock/vendas-10.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-precos-pvp-stock/vendas-10.xlsx
@@ -437,7 +437,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 26/10/2026, 10:45</v>
+        <v>Gerado em: 26/10/2026, 11:04</v>
       </c>
     </row>
     <row r="5">

--- a/docs/validacao-visual/2026-10-vendas-precos-pvp-stock/vendas-10.xlsx
+++ b/docs/validacao-visual/2026-10-vendas-precos-pvp-stock/vendas-10.xlsx
@@ -437,7 +437,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Gerado em: 26/10/2026, 11:04</v>
+        <v>Gerado em: 26/10/2026, 11:39</v>
       </c>
     </row>
     <row r="5">
